--- a/output/pdf_financials_xlsx/URAI.xlsx
+++ b/output/pdf_financials_xlsx/URAI.xlsx
@@ -1923,10 +1923,10 @@
         <v>0.003871</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0.003871</v>
+        <v>0.190648</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0.003871</v>
+        <v>0.361611</v>
       </c>
     </row>
     <row r="93">
@@ -3125,7 +3125,11 @@
           <t>Warrants reserve 7</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E16" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/URAI.xlsx
+++ b/output/pdf_financials_xlsx/URAI.xlsx
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.174283</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.161407</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.368681</v>
       </c>
     </row>
     <row r="35">
@@ -1012,13 +1012,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.174283</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.161407</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.368681</v>
       </c>
     </row>
     <row r="37">
@@ -1204,13 +1204,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.174283</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.190529</v>
+        <v>0.029122</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.450433</v>
+        <v>0.08175200000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
